--- a/Subject Key.xlsx
+++ b/Subject Key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Todd Appleby\Documents\Fent\CoffeyBehavior_MouseEdition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mr.Coffey\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6053B508-875B-4BB3-8335-A8A0FCB9C41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF41DC0-6B36-4A8E-8B05-BACD6D32EEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="116">
   <si>
     <t>TagNumber</t>
   </si>
@@ -254,9 +254,6 @@
     <t>BrainStorage</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>T1</t>
   </si>
   <si>
@@ -311,9 +308,6 @@
     <t>{5}</t>
   </si>
   <si>
-    <t>manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column</t>
-  </si>
-  <si>
     <t>old mouse (15 weeks); no video pretraining day 1; Data mixup on day 2</t>
   </si>
   <si>
@@ -332,26 +326,74 @@
     <t>C00358115</t>
   </si>
   <si>
-    <t xml:space="preserve">manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
-  </si>
-  <si>
-    <t>manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  Self admin macro ran on session 23 (extinction session), so third extinction week added</t>
-  </si>
-  <si>
-    <t>manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.   Self admin macro ran on session 23 (extinction session), so third extinction week added</t>
-  </si>
-  <si>
-    <t>manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  escaped box on session 20 &amp; 21.   Self admin macro ran on session 23 (extinction session), so third extinction week added</t>
-  </si>
-  <si>
-    <t>manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  escaped box on session 21.   Self admin macro ran on session 23 (extinction session), so third extinction week added</t>
+    <t>in PBS w/ Azide (change next on 11/25)</t>
+  </si>
+  <si>
+    <t>in Deli Fridge</t>
+  </si>
+  <si>
+    <t>cleared (iDISCO)</t>
+  </si>
+  <si>
+    <t>lightsheet room or Lukas's desk</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>Reinstatement+30m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, non-acq, manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, collected for pixel-seq, used for pixel-seq, manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, collected for pixel-seq, not used for pixel-seq, manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t>{5, 6, 23}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, REI Macro on week two of EXT, collected for pixel-seq, not used for pixel-seq, manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t>{5, 23}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, REI Macro on week two of EXT, collected for pixel-seq, used for pixel-seq, manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra week of extinction, REI Macro on week two of EXT, collected for pixel-seq, used for pixel-seq,  manual lever pressing on session 5 &amp; 6 as indicated in RemoveSessions column.  Session 7 used sugar-water baiting on the cue light as indicated in RemoveSessions column.  </t>
+  </si>
+  <si>
+    <t>{5, 6, 7, 23}</t>
+  </si>
+  <si>
+    <t>{5 ,23}</t>
+  </si>
+  <si>
+    <t>Extra week of extinction, REI Macro on week two of EXT, collected for pixel-seq, not used for pixel-seq</t>
+  </si>
+  <si>
+    <t>Three weeks of extinction</t>
+  </si>
+  <si>
+    <t>Three weeks of extinction, non-acq</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,8 +419,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,8 +440,14 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -415,16 +470,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -432,6 +499,10 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,35 +820,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X140"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" customWidth="1"/>
-    <col min="14" max="15" width="22.28515625" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" customWidth="1"/>
+    <col min="14" max="15" width="22.33203125" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -851,7 +922,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -897,6 +968,9 @@
       <c r="O2" t="b">
         <v>0</v>
       </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
       <c r="Q2" t="s">
         <v>66</v>
       </c>
@@ -906,17 +980,23 @@
       <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="2">
+      <c r="T2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V2" s="7">
         <v>0.38541666666666669</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W2" s="7">
         <v>0.44791666666666669</v>
       </c>
       <c r="X2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -962,6 +1042,9 @@
       <c r="O3" t="b">
         <v>0</v>
       </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
       <c r="Q3" t="s">
         <v>66</v>
       </c>
@@ -971,17 +1054,23 @@
       <c r="S3" t="s">
         <v>27</v>
       </c>
-      <c r="V3" s="2">
+      <c r="T3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U3" t="s">
+        <v>97</v>
+      </c>
+      <c r="V3" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="7">
         <v>0.45833333333333331</v>
       </c>
       <c r="X3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1027,6 +1116,9 @@
       <c r="O4" t="b">
         <v>0</v>
       </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
       <c r="Q4" t="s">
         <v>66</v>
       </c>
@@ -1036,17 +1128,23 @@
       <c r="S4" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="2">
+      <c r="T4" t="s">
+        <v>96</v>
+      </c>
+      <c r="U4" t="s">
+        <v>97</v>
+      </c>
+      <c r="V4" s="7">
         <v>0.40625</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="7">
         <v>0.46875</v>
       </c>
       <c r="X4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1092,6 +1190,9 @@
       <c r="O5" t="b">
         <v>0</v>
       </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
       <c r="Q5" t="s">
         <v>66</v>
       </c>
@@ -1101,17 +1202,23 @@
       <c r="S5" t="s">
         <v>27</v>
       </c>
-      <c r="V5" s="2">
+      <c r="T5" t="s">
+        <v>96</v>
+      </c>
+      <c r="U5" t="s">
+        <v>97</v>
+      </c>
+      <c r="V5" s="7">
         <v>0.41666666666666702</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="7">
         <v>0.47916666666666702</v>
       </c>
       <c r="X5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1157,6 +1264,9 @@
       <c r="O6" t="b">
         <v>0</v>
       </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
       <c r="Q6" t="s">
         <v>66</v>
       </c>
@@ -1166,17 +1276,23 @@
       <c r="S6" t="s">
         <v>27</v>
       </c>
-      <c r="V6" s="2">
+      <c r="T6" t="s">
+        <v>96</v>
+      </c>
+      <c r="U6" t="s">
+        <v>97</v>
+      </c>
+      <c r="V6" s="7">
         <v>0.42708333333333298</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" s="7">
         <v>0.48958333333333298</v>
       </c>
       <c r="X6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1222,6 +1338,9 @@
       <c r="O7" t="b">
         <v>0</v>
       </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
       <c r="Q7" t="s">
         <v>66</v>
       </c>
@@ -1231,17 +1350,23 @@
       <c r="S7" t="s">
         <v>27</v>
       </c>
-      <c r="V7" s="2">
+      <c r="T7" t="s">
+        <v>96</v>
+      </c>
+      <c r="U7" t="s">
+        <v>97</v>
+      </c>
+      <c r="V7" s="7">
         <v>0.4375</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7" s="7">
         <v>0.5</v>
       </c>
       <c r="X7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1287,6 +1412,9 @@
       <c r="O8" t="b">
         <v>0</v>
       </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
       <c r="Q8" t="s">
         <v>66</v>
       </c>
@@ -1296,17 +1424,23 @@
       <c r="S8" t="s">
         <v>27</v>
       </c>
-      <c r="V8" s="2">
+      <c r="T8" t="s">
+        <v>96</v>
+      </c>
+      <c r="U8" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="7">
         <v>0.44791666666666602</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="7">
         <v>0.51041666666666696</v>
       </c>
       <c r="X8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1352,6 +1486,9 @@
       <c r="O9" t="b">
         <v>0</v>
       </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
       <c r="Q9" t="s">
         <v>66</v>
       </c>
@@ -1361,17 +1498,23 @@
       <c r="S9" t="s">
         <v>27</v>
       </c>
-      <c r="V9" s="2">
+      <c r="T9" t="s">
+        <v>96</v>
+      </c>
+      <c r="U9" t="s">
+        <v>97</v>
+      </c>
+      <c r="V9" s="7">
         <v>0.45833333333333298</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="7">
         <v>0.52083333333333304</v>
       </c>
       <c r="X9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1417,6 +1560,9 @@
       <c r="O10" t="b">
         <v>0</v>
       </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
       <c r="Q10" t="s">
         <v>66</v>
       </c>
@@ -1426,17 +1572,23 @@
       <c r="S10" t="s">
         <v>27</v>
       </c>
-      <c r="V10" s="2">
+      <c r="T10" t="s">
+        <v>96</v>
+      </c>
+      <c r="U10" t="s">
+        <v>97</v>
+      </c>
+      <c r="V10" s="7">
         <v>0.53125</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W10" s="7">
         <v>0.59375</v>
       </c>
       <c r="X10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1482,6 +1634,9 @@
       <c r="O11" t="b">
         <v>0</v>
       </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
       <c r="Q11" t="s">
         <v>66</v>
       </c>
@@ -1491,17 +1646,23 @@
       <c r="S11" t="s">
         <v>27</v>
       </c>
-      <c r="V11" s="2">
+      <c r="T11" t="s">
+        <v>96</v>
+      </c>
+      <c r="U11" t="s">
+        <v>97</v>
+      </c>
+      <c r="V11" s="7">
         <v>0.54166666666666696</v>
       </c>
-      <c r="W11" s="2">
+      <c r="W11" s="7">
         <v>0.60416666666666696</v>
       </c>
       <c r="X11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1547,6 +1708,9 @@
       <c r="O12" t="b">
         <v>0</v>
       </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
       <c r="Q12" t="s">
         <v>66</v>
       </c>
@@ -1556,17 +1720,23 @@
       <c r="S12" t="s">
         <v>27</v>
       </c>
-      <c r="V12" s="2">
+      <c r="T12" t="s">
+        <v>96</v>
+      </c>
+      <c r="U12" t="s">
+        <v>97</v>
+      </c>
+      <c r="V12" s="7">
         <v>0.55208333333333304</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="7">
         <v>0.61458333333333304</v>
       </c>
       <c r="X12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1612,6 +1782,9 @@
       <c r="O13" t="b">
         <v>0</v>
       </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
       <c r="Q13" t="s">
         <v>66</v>
       </c>
@@ -1621,17 +1794,23 @@
       <c r="S13" t="s">
         <v>27</v>
       </c>
-      <c r="V13" s="2">
+      <c r="T13" t="s">
+        <v>96</v>
+      </c>
+      <c r="U13" t="s">
+        <v>97</v>
+      </c>
+      <c r="V13" s="7">
         <v>0.5625</v>
       </c>
-      <c r="W13" s="2">
+      <c r="W13" s="7">
         <v>0.625</v>
       </c>
       <c r="X13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1677,6 +1856,9 @@
       <c r="O14" t="b">
         <v>0</v>
       </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
       <c r="Q14" t="s">
         <v>66</v>
       </c>
@@ -1686,17 +1868,23 @@
       <c r="S14" t="s">
         <v>27</v>
       </c>
-      <c r="V14" s="2">
+      <c r="T14" t="s">
+        <v>96</v>
+      </c>
+      <c r="U14" t="s">
+        <v>97</v>
+      </c>
+      <c r="V14" s="7">
         <v>0.57291666666666696</v>
       </c>
-      <c r="W14" s="2">
+      <c r="W14" s="7">
         <v>0.63541666666666696</v>
       </c>
       <c r="X14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -1742,6 +1930,9 @@
       <c r="O15" t="b">
         <v>0</v>
       </c>
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
       <c r="Q15" t="s">
         <v>66</v>
       </c>
@@ -1751,17 +1942,23 @@
       <c r="S15" t="s">
         <v>27</v>
       </c>
-      <c r="V15" s="2">
+      <c r="T15" t="s">
+        <v>96</v>
+      </c>
+      <c r="U15" t="s">
+        <v>97</v>
+      </c>
+      <c r="V15" s="7">
         <v>0.58333333333333304</v>
       </c>
-      <c r="W15" s="2">
+      <c r="W15" s="7">
         <v>0.64583333333333304</v>
       </c>
       <c r="X15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1807,6 +2004,9 @@
       <c r="O16" t="b">
         <v>0</v>
       </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
       <c r="Q16" t="s">
         <v>66</v>
       </c>
@@ -1816,17 +2016,23 @@
       <c r="S16" t="s">
         <v>27</v>
       </c>
-      <c r="V16" s="2">
+      <c r="T16" t="s">
+        <v>96</v>
+      </c>
+      <c r="U16" t="s">
+        <v>97</v>
+      </c>
+      <c r="V16" s="7">
         <v>0.59375</v>
       </c>
-      <c r="W16" s="2">
+      <c r="W16" s="7">
         <v>0.65625</v>
       </c>
       <c r="X16" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1872,6 +2078,9 @@
       <c r="O17" t="b">
         <v>0</v>
       </c>
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
       <c r="Q17" t="s">
         <v>66</v>
       </c>
@@ -1881,17 +2090,23 @@
       <c r="S17" t="s">
         <v>27</v>
       </c>
-      <c r="V17" s="2">
+      <c r="T17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V17" s="7">
         <v>0.60416666666666696</v>
       </c>
-      <c r="W17" s="2">
+      <c r="W17" s="7">
         <v>0.66666666666666696</v>
       </c>
       <c r="X17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>651</v>
       </c>
@@ -1937,6 +2152,9 @@
       <c r="O18" t="b">
         <v>1</v>
       </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
       <c r="Q18" t="s">
         <v>66</v>
       </c>
@@ -1946,17 +2164,23 @@
       <c r="S18" t="s">
         <v>56</v>
       </c>
-      <c r="V18" s="3">
+      <c r="T18" t="s">
+        <v>98</v>
+      </c>
+      <c r="U18" t="s">
+        <v>99</v>
+      </c>
+      <c r="V18" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="8">
         <v>0.45833333333333331</v>
       </c>
       <c r="X18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>652</v>
       </c>
@@ -2002,6 +2226,9 @@
       <c r="O19" t="b">
         <v>1</v>
       </c>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
       <c r="Q19" t="s">
         <v>66</v>
       </c>
@@ -2011,17 +2238,23 @@
       <c r="S19" t="s">
         <v>56</v>
       </c>
-      <c r="V19" s="4">
+      <c r="T19" t="s">
+        <v>98</v>
+      </c>
+      <c r="U19" t="s">
+        <v>99</v>
+      </c>
+      <c r="V19" s="9">
         <v>0.40625</v>
       </c>
-      <c r="W19" s="4">
+      <c r="W19" s="9">
         <v>0.46875</v>
       </c>
       <c r="X19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>655</v>
       </c>
@@ -2067,6 +2300,9 @@
       <c r="O20" t="b">
         <v>1</v>
       </c>
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
       <c r="Q20" t="s">
         <v>66</v>
       </c>
@@ -2076,17 +2312,23 @@
       <c r="S20" t="s">
         <v>56</v>
       </c>
-      <c r="V20" s="3">
+      <c r="T20" t="s">
+        <v>98</v>
+      </c>
+      <c r="U20" t="s">
+        <v>99</v>
+      </c>
+      <c r="V20" s="8">
         <v>0.41666666666666702</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="8">
         <v>0.47916666666666702</v>
       </c>
       <c r="X20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>656</v>
       </c>
@@ -2132,6 +2374,9 @@
       <c r="O21" t="b">
         <v>1</v>
       </c>
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
       <c r="Q21" t="s">
         <v>66</v>
       </c>
@@ -2141,17 +2386,23 @@
       <c r="S21" t="s">
         <v>56</v>
       </c>
-      <c r="V21" s="4">
+      <c r="T21" t="s">
+        <v>98</v>
+      </c>
+      <c r="U21" t="s">
+        <v>99</v>
+      </c>
+      <c r="V21" s="9">
         <v>0.42708333333333298</v>
       </c>
-      <c r="W21" s="4">
+      <c r="W21" s="9">
         <v>0.48958333333333298</v>
       </c>
       <c r="X21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>659</v>
       </c>
@@ -2197,6 +2448,9 @@
       <c r="O22" t="b">
         <v>1</v>
       </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
       <c r="Q22" t="s">
         <v>66</v>
       </c>
@@ -2206,17 +2460,23 @@
       <c r="S22" t="s">
         <v>56</v>
       </c>
-      <c r="V22" s="3">
+      <c r="T22" t="s">
+        <v>96</v>
+      </c>
+      <c r="U22" t="s">
+        <v>97</v>
+      </c>
+      <c r="V22" s="8">
         <v>0.4375</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="8">
         <v>0.5</v>
       </c>
       <c r="X22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>660</v>
       </c>
@@ -2262,6 +2522,9 @@
       <c r="O23" t="b">
         <v>1</v>
       </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
       <c r="Q23" t="s">
         <v>66</v>
       </c>
@@ -2271,17 +2534,23 @@
       <c r="S23" t="s">
         <v>56</v>
       </c>
-      <c r="V23" s="4">
+      <c r="T23" t="s">
+        <v>96</v>
+      </c>
+      <c r="U23" t="s">
+        <v>97</v>
+      </c>
+      <c r="V23" s="9">
         <v>0.44791666666666602</v>
       </c>
-      <c r="W23" s="4">
+      <c r="W23" s="9">
         <v>0.51041666666666696</v>
       </c>
       <c r="X23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>663</v>
       </c>
@@ -2327,6 +2596,9 @@
       <c r="O24" t="b">
         <v>1</v>
       </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
       <c r="Q24" t="s">
         <v>66</v>
       </c>
@@ -2336,17 +2608,23 @@
       <c r="S24" t="s">
         <v>56</v>
       </c>
-      <c r="V24" s="3">
+      <c r="T24" t="s">
+        <v>96</v>
+      </c>
+      <c r="U24" t="s">
+        <v>97</v>
+      </c>
+      <c r="V24" s="8">
         <v>0.45833333333333298</v>
       </c>
-      <c r="W24" s="3">
+      <c r="W24" s="8">
         <v>0.52083333333333304</v>
       </c>
       <c r="X24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>664</v>
       </c>
@@ -2392,6 +2670,9 @@
       <c r="O25" t="b">
         <v>1</v>
       </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
       <c r="Q25" t="s">
         <v>66</v>
       </c>
@@ -2401,17 +2682,23 @@
       <c r="S25" t="s">
         <v>56</v>
       </c>
-      <c r="V25" s="4">
+      <c r="T25" t="s">
+        <v>96</v>
+      </c>
+      <c r="U25" t="s">
+        <v>97</v>
+      </c>
+      <c r="V25" s="9">
         <v>0.46875</v>
       </c>
-      <c r="W25" s="3">
+      <c r="W25" s="8">
         <v>0.53125</v>
       </c>
       <c r="X25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>653</v>
       </c>
@@ -2457,6 +2744,9 @@
       <c r="O26" t="b">
         <v>1</v>
       </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
       <c r="Q26" t="s">
         <v>66</v>
       </c>
@@ -2466,17 +2756,23 @@
       <c r="S26" t="s">
         <v>56</v>
       </c>
-      <c r="V26" s="4">
+      <c r="T26" t="s">
+        <v>98</v>
+      </c>
+      <c r="U26" t="s">
+        <v>99</v>
+      </c>
+      <c r="V26" s="9">
         <v>0.53125</v>
       </c>
-      <c r="W26" s="4">
+      <c r="W26" s="9">
         <v>0.59375</v>
       </c>
       <c r="X26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>654</v>
       </c>
@@ -2522,6 +2818,9 @@
       <c r="O27" t="b">
         <v>1</v>
       </c>
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
       <c r="Q27" t="s">
         <v>66</v>
       </c>
@@ -2531,17 +2830,23 @@
       <c r="S27" t="s">
         <v>56</v>
       </c>
-      <c r="V27" s="3">
+      <c r="T27" t="s">
+        <v>98</v>
+      </c>
+      <c r="U27" t="s">
+        <v>99</v>
+      </c>
+      <c r="V27" s="8">
         <v>0.54166666666666696</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="8">
         <v>0.60416666666666696</v>
       </c>
       <c r="X27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>657</v>
       </c>
@@ -2587,6 +2892,9 @@
       <c r="O28" t="b">
         <v>1</v>
       </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
       <c r="Q28" t="s">
         <v>66</v>
       </c>
@@ -2596,17 +2904,23 @@
       <c r="S28" t="s">
         <v>56</v>
       </c>
-      <c r="V28" s="4">
+      <c r="T28" t="s">
+        <v>98</v>
+      </c>
+      <c r="U28" t="s">
+        <v>99</v>
+      </c>
+      <c r="V28" s="9">
         <v>0.55208333333333304</v>
       </c>
-      <c r="W28" s="4">
+      <c r="W28" s="9">
         <v>0.61458333333333304</v>
       </c>
       <c r="X28" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>658</v>
       </c>
@@ -2652,6 +2966,9 @@
       <c r="O29" t="b">
         <v>1</v>
       </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
       <c r="Q29" t="s">
         <v>66</v>
       </c>
@@ -2661,17 +2978,23 @@
       <c r="S29" t="s">
         <v>56</v>
       </c>
-      <c r="V29" s="3">
+      <c r="T29" t="s">
+        <v>98</v>
+      </c>
+      <c r="U29" t="s">
+        <v>99</v>
+      </c>
+      <c r="V29" s="8">
         <v>0.5625</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="8">
         <v>0.625</v>
       </c>
       <c r="X29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>661</v>
       </c>
@@ -2717,6 +3040,9 @@
       <c r="O30" t="b">
         <v>1</v>
       </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
       <c r="Q30" t="s">
         <v>66</v>
       </c>
@@ -2726,17 +3052,23 @@
       <c r="S30" t="s">
         <v>56</v>
       </c>
-      <c r="V30" s="4">
+      <c r="T30" t="s">
+        <v>96</v>
+      </c>
+      <c r="U30" t="s">
+        <v>97</v>
+      </c>
+      <c r="V30" s="9">
         <v>0.57291666666666696</v>
       </c>
-      <c r="W30" s="4">
+      <c r="W30" s="9">
         <v>0.63541666666666696</v>
       </c>
       <c r="X30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>662</v>
       </c>
@@ -2782,6 +3114,9 @@
       <c r="O31" t="b">
         <v>1</v>
       </c>
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
       <c r="Q31" t="s">
         <v>66</v>
       </c>
@@ -2791,17 +3126,23 @@
       <c r="S31" t="s">
         <v>56</v>
       </c>
-      <c r="V31" s="3">
+      <c r="T31" t="s">
+        <v>96</v>
+      </c>
+      <c r="U31" t="s">
+        <v>97</v>
+      </c>
+      <c r="V31" s="8">
         <v>0.58333333333333304</v>
       </c>
-      <c r="W31" s="3">
+      <c r="W31" s="8">
         <v>0.64583333333333304</v>
       </c>
       <c r="X31" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>665</v>
       </c>
@@ -2847,6 +3188,9 @@
       <c r="O32" t="b">
         <v>1</v>
       </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
       <c r="Q32" t="s">
         <v>66</v>
       </c>
@@ -2856,17 +3200,23 @@
       <c r="S32" t="s">
         <v>56</v>
       </c>
-      <c r="V32" s="4">
+      <c r="T32" t="s">
+        <v>96</v>
+      </c>
+      <c r="U32" t="s">
+        <v>97</v>
+      </c>
+      <c r="V32" s="9">
         <v>0.59375</v>
       </c>
-      <c r="W32" s="4">
+      <c r="W32" s="9">
         <v>0.65625</v>
       </c>
       <c r="X32" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>666</v>
       </c>
@@ -2912,6 +3262,9 @@
       <c r="O33" t="b">
         <v>1</v>
       </c>
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
       <c r="Q33" t="s">
         <v>66</v>
       </c>
@@ -2921,17 +3274,23 @@
       <c r="S33" t="s">
         <v>56</v>
       </c>
-      <c r="V33" s="3">
+      <c r="T33" t="s">
+        <v>96</v>
+      </c>
+      <c r="U33" t="s">
+        <v>97</v>
+      </c>
+      <c r="V33" s="8">
         <v>0.60416666666666696</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W33" s="8">
         <v>0.66666666666666696</v>
       </c>
       <c r="X33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -2941,7 +3300,7 @@
       <c r="C34">
         <v>3</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E34" s="1">
@@ -2977,20 +3336,32 @@
       <c r="O34" t="b">
         <v>0</v>
       </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
       <c r="Q34" t="s">
         <v>66</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
-      <c r="V34" s="2">
+      <c r="S34" t="s">
+        <v>56</v>
+      </c>
+      <c r="T34" t="s">
+        <v>98</v>
+      </c>
+      <c r="U34" t="s">
+        <v>99</v>
+      </c>
+      <c r="V34" s="7">
         <v>0.375</v>
       </c>
-      <c r="W34" s="2">
+      <c r="W34" s="7">
         <v>0.4375</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2</v>
       </c>
@@ -3000,7 +3371,7 @@
       <c r="C35">
         <v>3</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="1">
@@ -3036,14 +3407,32 @@
       <c r="O35" t="b">
         <v>0</v>
       </c>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
       <c r="Q35" t="s">
         <v>66</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S35" t="s">
+        <v>56</v>
+      </c>
+      <c r="T35" t="s">
+        <v>100</v>
+      </c>
+      <c r="U35" t="s">
+        <v>100</v>
+      </c>
+      <c r="V35" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -3053,7 +3442,7 @@
       <c r="C36">
         <v>3</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E36" s="1">
@@ -3089,20 +3478,32 @@
       <c r="O36" t="b">
         <v>0</v>
       </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
       <c r="Q36" t="s">
         <v>66</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
-      <c r="V36" s="2">
+      <c r="S36" t="s">
+        <v>56</v>
+      </c>
+      <c r="T36" t="s">
+        <v>98</v>
+      </c>
+      <c r="U36" t="s">
+        <v>99</v>
+      </c>
+      <c r="V36" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="W36" s="2">
+      <c r="W36" s="7">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>4</v>
       </c>
@@ -3112,7 +3513,7 @@
       <c r="C37">
         <v>3</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E37" s="1">
@@ -3148,14 +3549,32 @@
       <c r="O37" t="b">
         <v>0</v>
       </c>
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
       <c r="Q37" t="s">
         <v>66</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S37" t="s">
+        <v>56</v>
+      </c>
+      <c r="T37" t="s">
+        <v>98</v>
+      </c>
+      <c r="U37" t="s">
+        <v>99</v>
+      </c>
+      <c r="V37" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W37" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>5</v>
       </c>
@@ -3165,7 +3584,7 @@
       <c r="C38">
         <v>3</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E38" s="1">
@@ -3201,20 +3620,32 @@
       <c r="O38" t="b">
         <v>0</v>
       </c>
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
       <c r="Q38" t="s">
         <v>66</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
-      <c r="V38" s="2">
+      <c r="S38" t="s">
+        <v>56</v>
+      </c>
+      <c r="T38" t="s">
+        <v>98</v>
+      </c>
+      <c r="U38" t="s">
+        <v>99</v>
+      </c>
+      <c r="V38" s="7">
         <v>0.41666666666666669</v>
       </c>
-      <c r="W38" s="2">
+      <c r="W38" s="7">
         <v>0.47916666666666669</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3224,7 +3655,7 @@
       <c r="C39">
         <v>3</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E39" s="1">
@@ -3260,14 +3691,32 @@
       <c r="O39" t="b">
         <v>0</v>
       </c>
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
       <c r="Q39" t="s">
         <v>66</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S39" t="s">
+        <v>56</v>
+      </c>
+      <c r="T39" t="s">
+        <v>98</v>
+      </c>
+      <c r="U39" t="s">
+        <v>99</v>
+      </c>
+      <c r="V39" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>7</v>
       </c>
@@ -3277,7 +3726,7 @@
       <c r="C40">
         <v>3</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="1">
@@ -3313,20 +3762,32 @@
       <c r="O40" t="b">
         <v>0</v>
       </c>
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
       <c r="Q40" t="s">
         <v>66</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
-      <c r="V40" s="2">
+      <c r="S40" t="s">
+        <v>56</v>
+      </c>
+      <c r="T40" t="s">
+        <v>98</v>
+      </c>
+      <c r="U40" t="s">
+        <v>99</v>
+      </c>
+      <c r="V40" s="7">
         <v>0.4375</v>
       </c>
-      <c r="W40" s="2">
+      <c r="W40" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>8</v>
       </c>
@@ -3336,7 +3797,7 @@
       <c r="C41">
         <v>3</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E41" s="1">
@@ -3372,14 +3833,32 @@
       <c r="O41" t="b">
         <v>0</v>
       </c>
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
       <c r="Q41" t="s">
         <v>66</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S41" t="s">
+        <v>56</v>
+      </c>
+      <c r="T41" t="s">
+        <v>98</v>
+      </c>
+      <c r="U41" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V41" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="W41" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>9</v>
       </c>
@@ -3389,7 +3868,7 @@
       <c r="C42">
         <v>3</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E42" s="1">
@@ -3425,20 +3904,32 @@
       <c r="O42" t="b">
         <v>0</v>
       </c>
+      <c r="P42" t="b">
+        <v>1</v>
+      </c>
       <c r="Q42" t="s">
         <v>66</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
-      <c r="V42" s="2">
+      <c r="S42" t="s">
+        <v>56</v>
+      </c>
+      <c r="T42" t="s">
+        <v>98</v>
+      </c>
+      <c r="U42" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V42" s="7">
         <v>0.5</v>
       </c>
-      <c r="W42" s="2">
+      <c r="W42" s="7">
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>10</v>
       </c>
@@ -3448,7 +3939,7 @@
       <c r="C43">
         <v>3</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E43" s="1">
@@ -3484,14 +3975,32 @@
       <c r="O43" t="b">
         <v>0</v>
       </c>
+      <c r="P43" t="b">
+        <v>1</v>
+      </c>
       <c r="Q43" t="s">
         <v>66</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S43" t="s">
+        <v>56</v>
+      </c>
+      <c r="T43" t="s">
+        <v>98</v>
+      </c>
+      <c r="U43" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V43" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>11</v>
       </c>
@@ -3501,7 +4010,7 @@
       <c r="C44">
         <v>3</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E44" s="1">
@@ -3537,20 +4046,32 @@
       <c r="O44" t="b">
         <v>0</v>
       </c>
+      <c r="P44" t="b">
+        <v>1</v>
+      </c>
       <c r="Q44" t="s">
         <v>66</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
-      <c r="V44" s="2">
+      <c r="S44" t="s">
+        <v>56</v>
+      </c>
+      <c r="T44" t="s">
+        <v>98</v>
+      </c>
+      <c r="U44" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V44" s="7">
         <v>0.52083333333333337</v>
       </c>
-      <c r="W44" s="2">
+      <c r="W44" s="7">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>12</v>
       </c>
@@ -3560,7 +4081,7 @@
       <c r="C45">
         <v>3</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E45" s="1">
@@ -3596,14 +4117,32 @@
       <c r="O45" t="b">
         <v>0</v>
       </c>
+      <c r="P45" t="b">
+        <v>1</v>
+      </c>
       <c r="Q45" t="s">
         <v>66</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S45" t="s">
+        <v>56</v>
+      </c>
+      <c r="T45" t="s">
+        <v>98</v>
+      </c>
+      <c r="U45" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V45" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="W45" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3613,7 +4152,7 @@
       <c r="C46">
         <v>3</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E46" s="1">
@@ -3649,20 +4188,32 @@
       <c r="O46" t="b">
         <v>0</v>
       </c>
+      <c r="P46" t="b">
+        <v>1</v>
+      </c>
       <c r="Q46" t="s">
         <v>66</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
-      <c r="V46" s="2">
+      <c r="S46" t="s">
+        <v>56</v>
+      </c>
+      <c r="T46" t="s">
+        <v>98</v>
+      </c>
+      <c r="U46" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V46" s="7">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="W46" s="2">
+      <c r="W46" s="7">
         <v>0.10416666666666667</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14</v>
       </c>
@@ -3672,7 +4223,7 @@
       <c r="C47">
         <v>3</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E47" s="1">
@@ -3708,14 +4259,32 @@
       <c r="O47" t="b">
         <v>0</v>
       </c>
+      <c r="P47" t="b">
+        <v>1</v>
+      </c>
       <c r="Q47" t="s">
         <v>66</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="S47" t="s">
+        <v>56</v>
+      </c>
+      <c r="T47" t="s">
+        <v>98</v>
+      </c>
+      <c r="U47" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V47" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W47" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>15</v>
       </c>
@@ -3725,7 +4294,7 @@
       <c r="C48">
         <v>3</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E48" s="1">
@@ -3761,20 +4330,32 @@
       <c r="O48" t="b">
         <v>0</v>
       </c>
+      <c r="P48" t="b">
+        <v>1</v>
+      </c>
       <c r="Q48" t="s">
         <v>66</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
-      <c r="V48" s="2">
+      <c r="S48" t="s">
+        <v>56</v>
+      </c>
+      <c r="T48" t="s">
+        <v>98</v>
+      </c>
+      <c r="U48" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V48" s="7">
         <v>6.25E-2</v>
       </c>
-      <c r="W48" s="2">
+      <c r="W48" s="7">
         <v>0.125</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>16</v>
       </c>
@@ -3784,7 +4365,7 @@
       <c r="C49">
         <v>3</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E49" s="1">
@@ -3820,14 +4401,32 @@
       <c r="O49" t="b">
         <v>0</v>
       </c>
+      <c r="P49" t="b">
+        <v>1</v>
+      </c>
       <c r="Q49" t="s">
         <v>66</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S49" t="s">
+        <v>56</v>
+      </c>
+      <c r="T49" t="s">
+        <v>98</v>
+      </c>
+      <c r="U49" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V49" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="W49" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>17</v>
       </c>
@@ -3867,14 +4466,32 @@
       <c r="O50" t="b">
         <v>0</v>
       </c>
+      <c r="P50" t="b">
+        <v>1</v>
+      </c>
       <c r="Q50" t="s">
         <v>66</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S50" t="s">
+        <v>56</v>
+      </c>
+      <c r="T50" t="s">
+        <v>96</v>
+      </c>
+      <c r="U50" t="s">
+        <v>97</v>
+      </c>
+      <c r="V50" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="W50" s="7">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>18</v>
       </c>
@@ -3914,14 +4531,32 @@
       <c r="O51" t="b">
         <v>0</v>
       </c>
+      <c r="P51" t="b">
+        <v>1</v>
+      </c>
       <c r="Q51" t="s">
         <v>66</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S51" t="s">
+        <v>56</v>
+      </c>
+      <c r="T51" t="s">
+        <v>96</v>
+      </c>
+      <c r="U51" t="s">
+        <v>97</v>
+      </c>
+      <c r="V51" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="W51" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>19</v>
       </c>
@@ -3961,14 +4596,32 @@
       <c r="O52" t="b">
         <v>0</v>
       </c>
+      <c r="P52" t="b">
+        <v>1</v>
+      </c>
       <c r="Q52" t="s">
         <v>66</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S52" t="s">
+        <v>56</v>
+      </c>
+      <c r="T52" t="s">
+        <v>96</v>
+      </c>
+      <c r="U52" t="s">
+        <v>97</v>
+      </c>
+      <c r="V52" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W52" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>20</v>
       </c>
@@ -4008,14 +4661,32 @@
       <c r="O53" t="b">
         <v>0</v>
       </c>
+      <c r="P53" t="b">
+        <v>1</v>
+      </c>
       <c r="Q53" t="s">
         <v>66</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S53" t="s">
+        <v>56</v>
+      </c>
+      <c r="T53" t="s">
+        <v>96</v>
+      </c>
+      <c r="U53" t="s">
+        <v>97</v>
+      </c>
+      <c r="V53" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W53" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>21</v>
       </c>
@@ -4055,14 +4726,32 @@
       <c r="O54" t="b">
         <v>0</v>
       </c>
+      <c r="P54" t="b">
+        <v>1</v>
+      </c>
       <c r="Q54" t="s">
         <v>66</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S54" t="s">
+        <v>56</v>
+      </c>
+      <c r="T54" t="s">
+        <v>96</v>
+      </c>
+      <c r="U54" t="s">
+        <v>97</v>
+      </c>
+      <c r="V54" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W54" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>22</v>
       </c>
@@ -4102,14 +4791,32 @@
       <c r="O55" t="b">
         <v>0</v>
       </c>
+      <c r="P55" t="b">
+        <v>1</v>
+      </c>
       <c r="Q55" t="s">
         <v>66</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S55" t="s">
+        <v>56</v>
+      </c>
+      <c r="T55" t="s">
+        <v>96</v>
+      </c>
+      <c r="U55" t="s">
+        <v>97</v>
+      </c>
+      <c r="V55" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W55" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>23</v>
       </c>
@@ -4149,14 +4856,32 @@
       <c r="O56" t="b">
         <v>0</v>
       </c>
+      <c r="P56" t="b">
+        <v>1</v>
+      </c>
       <c r="Q56" t="s">
         <v>66</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S56" t="s">
+        <v>56</v>
+      </c>
+      <c r="T56" t="s">
+        <v>96</v>
+      </c>
+      <c r="U56" t="s">
+        <v>97</v>
+      </c>
+      <c r="V56" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="W56" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>24</v>
       </c>
@@ -4196,14 +4921,32 @@
       <c r="O57" t="b">
         <v>0</v>
       </c>
+      <c r="P57" t="b">
+        <v>1</v>
+      </c>
       <c r="Q57" t="s">
         <v>66</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S57" t="s">
+        <v>56</v>
+      </c>
+      <c r="T57" t="s">
+        <v>96</v>
+      </c>
+      <c r="U57" t="s">
+        <v>97</v>
+      </c>
+      <c r="V57" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="W57" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>25</v>
       </c>
@@ -4243,14 +4986,32 @@
       <c r="O58" t="b">
         <v>0</v>
       </c>
+      <c r="P58" t="b">
+        <v>1</v>
+      </c>
       <c r="Q58" t="s">
         <v>66</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S58" t="s">
+        <v>56</v>
+      </c>
+      <c r="T58" t="s">
+        <v>96</v>
+      </c>
+      <c r="U58" t="s">
+        <v>97</v>
+      </c>
+      <c r="V58" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="W58" s="7">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>26</v>
       </c>
@@ -4290,14 +5051,32 @@
       <c r="O59" t="b">
         <v>0</v>
       </c>
+      <c r="P59" t="b">
+        <v>1</v>
+      </c>
       <c r="Q59" t="s">
         <v>66</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S59" t="s">
+        <v>56</v>
+      </c>
+      <c r="T59" t="s">
+        <v>96</v>
+      </c>
+      <c r="U59" t="s">
+        <v>97</v>
+      </c>
+      <c r="V59" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="W59" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>27</v>
       </c>
@@ -4337,14 +5116,32 @@
       <c r="O60" t="b">
         <v>0</v>
       </c>
+      <c r="P60" t="b">
+        <v>1</v>
+      </c>
       <c r="Q60" t="s">
         <v>66</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S60" t="s">
+        <v>56</v>
+      </c>
+      <c r="T60" t="s">
+        <v>96</v>
+      </c>
+      <c r="U60" t="s">
+        <v>97</v>
+      </c>
+      <c r="V60" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="W60" s="7">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>28</v>
       </c>
@@ -4384,14 +5181,32 @@
       <c r="O61" t="b">
         <v>0</v>
       </c>
+      <c r="P61" t="b">
+        <v>1</v>
+      </c>
       <c r="Q61" t="s">
         <v>66</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S61" t="s">
+        <v>56</v>
+      </c>
+      <c r="T61" t="s">
+        <v>96</v>
+      </c>
+      <c r="U61" t="s">
+        <v>97</v>
+      </c>
+      <c r="V61" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="W61" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>29</v>
       </c>
@@ -4431,14 +5246,32 @@
       <c r="O62" t="b">
         <v>0</v>
       </c>
+      <c r="P62" t="b">
+        <v>1</v>
+      </c>
       <c r="Q62" t="s">
         <v>66</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S62" t="s">
+        <v>56</v>
+      </c>
+      <c r="T62" t="s">
+        <v>96</v>
+      </c>
+      <c r="U62" t="s">
+        <v>97</v>
+      </c>
+      <c r="V62" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W62" s="7">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>30</v>
       </c>
@@ -4478,14 +5311,32 @@
       <c r="O63" t="b">
         <v>0</v>
       </c>
+      <c r="P63" t="b">
+        <v>1</v>
+      </c>
       <c r="Q63" t="s">
         <v>66</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S63" t="s">
+        <v>56</v>
+      </c>
+      <c r="T63" t="s">
+        <v>96</v>
+      </c>
+      <c r="U63" t="s">
+        <v>97</v>
+      </c>
+      <c r="V63" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W63" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>31</v>
       </c>
@@ -4525,14 +5376,32 @@
       <c r="O64" t="b">
         <v>0</v>
       </c>
+      <c r="P64" t="b">
+        <v>1</v>
+      </c>
       <c r="Q64" t="s">
         <v>66</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S64" t="s">
+        <v>56</v>
+      </c>
+      <c r="T64" t="s">
+        <v>96</v>
+      </c>
+      <c r="U64" t="s">
+        <v>97</v>
+      </c>
+      <c r="V64" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="W64" s="7">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>32</v>
       </c>
@@ -4572,14 +5441,32 @@
       <c r="O65" t="b">
         <v>0</v>
       </c>
+      <c r="P65" t="b">
+        <v>1</v>
+      </c>
       <c r="Q65" t="s">
         <v>66</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S65" t="s">
+        <v>56</v>
+      </c>
+      <c r="T65" t="s">
+        <v>96</v>
+      </c>
+      <c r="U65" t="s">
+        <v>97</v>
+      </c>
+      <c r="V65" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="W65" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>33</v>
       </c>
@@ -4619,14 +5506,32 @@
       <c r="O66" t="b">
         <v>0</v>
       </c>
+      <c r="P66" t="b">
+        <v>1</v>
+      </c>
       <c r="Q66" t="s">
         <v>69</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S66" t="s">
+        <v>27</v>
+      </c>
+      <c r="T66" t="s">
+        <v>96</v>
+      </c>
+      <c r="U66" t="s">
+        <v>97</v>
+      </c>
+      <c r="V66" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="W66" s="8">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>34</v>
       </c>
@@ -4666,14 +5571,32 @@
       <c r="O67" t="b">
         <v>0</v>
       </c>
+      <c r="P67" t="b">
+        <v>1</v>
+      </c>
       <c r="Q67" t="s">
         <v>69</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S67" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" t="s">
+        <v>96</v>
+      </c>
+      <c r="U67" t="s">
+        <v>97</v>
+      </c>
+      <c r="V67" s="7">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="W67" s="9">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>35</v>
       </c>
@@ -4713,14 +5636,32 @@
       <c r="O68" t="b">
         <v>0</v>
       </c>
+      <c r="P68" t="b">
+        <v>1</v>
+      </c>
       <c r="Q68" t="s">
         <v>69</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S68" t="s">
+        <v>27</v>
+      </c>
+      <c r="T68" t="s">
+        <v>96</v>
+      </c>
+      <c r="U68" t="s">
+        <v>97</v>
+      </c>
+      <c r="V68" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W68" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>36</v>
       </c>
@@ -4760,14 +5701,32 @@
       <c r="O69" t="b">
         <v>0</v>
       </c>
+      <c r="P69" t="b">
+        <v>1</v>
+      </c>
       <c r="Q69" t="s">
         <v>68</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S69" t="s">
+        <v>27</v>
+      </c>
+      <c r="T69" t="s">
+        <v>96</v>
+      </c>
+      <c r="U69" t="s">
+        <v>97</v>
+      </c>
+      <c r="V69" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="W69" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>37</v>
       </c>
@@ -4807,14 +5766,32 @@
       <c r="O70" t="b">
         <v>0</v>
       </c>
+      <c r="P70" t="b">
+        <v>1</v>
+      </c>
       <c r="Q70" t="s">
         <v>69</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S70" t="s">
+        <v>27</v>
+      </c>
+      <c r="T70" t="s">
+        <v>96</v>
+      </c>
+      <c r="U70" t="s">
+        <v>97</v>
+      </c>
+      <c r="V70" s="7">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="W70" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>38</v>
       </c>
@@ -4854,14 +5831,32 @@
       <c r="O71" t="b">
         <v>0</v>
       </c>
+      <c r="P71" t="b">
+        <v>1</v>
+      </c>
       <c r="Q71" t="s">
         <v>68</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S71" t="s">
+        <v>27</v>
+      </c>
+      <c r="T71" t="s">
+        <v>96</v>
+      </c>
+      <c r="U71" t="s">
+        <v>97</v>
+      </c>
+      <c r="V71" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W71" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>39</v>
       </c>
@@ -4901,14 +5896,32 @@
       <c r="O72" t="b">
         <v>0</v>
       </c>
+      <c r="P72" t="b">
+        <v>1</v>
+      </c>
       <c r="Q72" t="s">
         <v>69</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S72" t="s">
+        <v>27</v>
+      </c>
+      <c r="T72" t="s">
+        <v>96</v>
+      </c>
+      <c r="U72" t="s">
+        <v>97</v>
+      </c>
+      <c r="V72" s="7">
+        <v>0.40625</v>
+      </c>
+      <c r="W72" s="8">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>40</v>
       </c>
@@ -4948,14 +5961,32 @@
       <c r="O73" t="b">
         <v>0</v>
       </c>
+      <c r="P73" t="b">
+        <v>1</v>
+      </c>
       <c r="Q73" t="s">
         <v>69</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S73" t="s">
+        <v>27</v>
+      </c>
+      <c r="T73" t="s">
+        <v>96</v>
+      </c>
+      <c r="U73" t="s">
+        <v>97</v>
+      </c>
+      <c r="V73" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W73" s="9">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>41</v>
       </c>
@@ -4995,14 +6026,32 @@
       <c r="O74" t="b">
         <v>0</v>
       </c>
+      <c r="P74" t="b">
+        <v>1</v>
+      </c>
       <c r="Q74" t="s">
         <v>69</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S74" t="s">
+        <v>27</v>
+      </c>
+      <c r="T74" t="s">
+        <v>96</v>
+      </c>
+      <c r="U74" t="s">
+        <v>97</v>
+      </c>
+      <c r="V74" s="7">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="W74" s="8">
+        <v>0.48958333333333331</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>42</v>
       </c>
@@ -5042,14 +6091,32 @@
       <c r="O75" t="b">
         <v>0</v>
       </c>
+      <c r="P75" t="b">
+        <v>1</v>
+      </c>
       <c r="Q75" t="s">
         <v>69</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S75" t="s">
+        <v>27</v>
+      </c>
+      <c r="T75" t="s">
+        <v>96</v>
+      </c>
+      <c r="U75" t="s">
+        <v>97</v>
+      </c>
+      <c r="V75" s="7">
+        <v>0.40625</v>
+      </c>
+      <c r="W75" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>43</v>
       </c>
@@ -5089,14 +6156,32 @@
       <c r="O76" t="b">
         <v>0</v>
       </c>
+      <c r="P76" t="b">
+        <v>1</v>
+      </c>
       <c r="Q76" t="s">
         <v>69</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S76" t="s">
+        <v>27</v>
+      </c>
+      <c r="T76" t="s">
+        <v>96</v>
+      </c>
+      <c r="U76" t="s">
+        <v>97</v>
+      </c>
+      <c r="V76" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W76" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>44</v>
       </c>
@@ -5136,14 +6221,32 @@
       <c r="O77" t="b">
         <v>0</v>
       </c>
+      <c r="P77" t="b">
+        <v>1</v>
+      </c>
       <c r="Q77" t="s">
         <v>69</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S77" t="s">
+        <v>27</v>
+      </c>
+      <c r="T77" t="s">
+        <v>96</v>
+      </c>
+      <c r="U77" t="s">
+        <v>97</v>
+      </c>
+      <c r="V77" s="7">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="W77" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>45</v>
       </c>
@@ -5183,14 +6286,32 @@
       <c r="O78" t="b">
         <v>0</v>
       </c>
+      <c r="P78" t="b">
+        <v>1</v>
+      </c>
       <c r="Q78" t="s">
         <v>69</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S78" t="s">
+        <v>27</v>
+      </c>
+      <c r="T78" t="s">
+        <v>96</v>
+      </c>
+      <c r="U78" t="s">
+        <v>97</v>
+      </c>
+      <c r="V78" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="W78" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>46</v>
       </c>
@@ -5230,14 +6351,32 @@
       <c r="O79" t="b">
         <v>0</v>
       </c>
+      <c r="P79" t="b">
+        <v>1</v>
+      </c>
       <c r="Q79" t="s">
         <v>69</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S79" t="s">
+        <v>27</v>
+      </c>
+      <c r="T79" t="s">
+        <v>96</v>
+      </c>
+      <c r="U79" t="s">
+        <v>97</v>
+      </c>
+      <c r="V79" s="7">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="W79" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>47</v>
       </c>
@@ -5277,14 +6416,32 @@
       <c r="O80" t="b">
         <v>0</v>
       </c>
+      <c r="P80" t="b">
+        <v>1</v>
+      </c>
       <c r="Q80" t="s">
         <v>69</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S80" t="s">
+        <v>27</v>
+      </c>
+      <c r="T80" t="s">
+        <v>96</v>
+      </c>
+      <c r="U80" t="s">
+        <v>97</v>
+      </c>
+      <c r="V80" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="W80" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>48</v>
       </c>
@@ -5324,14 +6481,32 @@
       <c r="O81" t="b">
         <v>0</v>
       </c>
+      <c r="P81" t="b">
+        <v>1</v>
+      </c>
       <c r="Q81" t="s">
         <v>69</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S81" t="s">
+        <v>27</v>
+      </c>
+      <c r="T81" t="s">
+        <v>96</v>
+      </c>
+      <c r="U81" t="s">
+        <v>97</v>
+      </c>
+      <c r="V81" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="W81" s="9">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>49</v>
       </c>
@@ -5371,14 +6546,32 @@
       <c r="O82" t="b">
         <v>0</v>
       </c>
+      <c r="P82" t="b">
+        <v>1</v>
+      </c>
       <c r="Q82" t="s">
         <v>69</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S82" t="s">
+        <v>27</v>
+      </c>
+      <c r="T82" t="s">
+        <v>96</v>
+      </c>
+      <c r="U82" t="s">
+        <v>97</v>
+      </c>
+      <c r="V82" s="7">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="W82" s="8">
+        <v>7.2916666666666671E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>50</v>
       </c>
@@ -5418,14 +6611,32 @@
       <c r="O83" t="b">
         <v>0</v>
       </c>
+      <c r="P83" t="b">
+        <v>1</v>
+      </c>
       <c r="Q83" t="s">
         <v>69</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S83" t="s">
+        <v>27</v>
+      </c>
+      <c r="T83" t="s">
+        <v>96</v>
+      </c>
+      <c r="U83" t="s">
+        <v>97</v>
+      </c>
+      <c r="V83" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="W83" s="9">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>51</v>
       </c>
@@ -5465,14 +6676,32 @@
       <c r="O84" t="b">
         <v>0</v>
       </c>
+      <c r="P84" t="b">
+        <v>1</v>
+      </c>
       <c r="Q84" t="s">
         <v>69</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S84" t="s">
+        <v>27</v>
+      </c>
+      <c r="T84" t="s">
+        <v>96</v>
+      </c>
+      <c r="U84" t="s">
+        <v>97</v>
+      </c>
+      <c r="V84" s="7">
+        <v>0.53125</v>
+      </c>
+      <c r="W84" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>52</v>
       </c>
@@ -5512,14 +6741,32 @@
       <c r="O85" t="b">
         <v>0</v>
       </c>
+      <c r="P85" t="b">
+        <v>1</v>
+      </c>
       <c r="Q85" t="s">
         <v>69</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S85" t="s">
+        <v>27</v>
+      </c>
+      <c r="T85" t="s">
+        <v>96</v>
+      </c>
+      <c r="U85" t="s">
+        <v>97</v>
+      </c>
+      <c r="V85" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W85" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>53</v>
       </c>
@@ -5559,14 +6806,32 @@
       <c r="O86" t="b">
         <v>0</v>
       </c>
+      <c r="P86" t="b">
+        <v>1</v>
+      </c>
       <c r="Q86" t="s">
         <v>69</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S86" t="s">
+        <v>27</v>
+      </c>
+      <c r="T86" t="s">
+        <v>96</v>
+      </c>
+      <c r="U86" t="s">
+        <v>97</v>
+      </c>
+      <c r="V86" s="7">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="W86" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>54</v>
       </c>
@@ -5606,14 +6871,32 @@
       <c r="O87" t="b">
         <v>0</v>
       </c>
+      <c r="P87" t="b">
+        <v>1</v>
+      </c>
       <c r="Q87" t="s">
         <v>69</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S87" t="s">
+        <v>27</v>
+      </c>
+      <c r="T87" t="s">
+        <v>96</v>
+      </c>
+      <c r="U87" t="s">
+        <v>97</v>
+      </c>
+      <c r="V87" s="7">
+        <v>0.53125</v>
+      </c>
+      <c r="W87" s="9">
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>55</v>
       </c>
@@ -5653,14 +6936,32 @@
       <c r="O88" t="b">
         <v>0</v>
       </c>
+      <c r="P88" t="b">
+        <v>1</v>
+      </c>
       <c r="Q88" t="s">
         <v>69</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S88" t="s">
+        <v>27</v>
+      </c>
+      <c r="T88" t="s">
+        <v>96</v>
+      </c>
+      <c r="U88" t="s">
+        <v>97</v>
+      </c>
+      <c r="V88" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W88" s="8">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>56</v>
       </c>
@@ -5700,14 +7001,32 @@
       <c r="O89" t="b">
         <v>0</v>
       </c>
+      <c r="P89" t="b">
+        <v>1</v>
+      </c>
       <c r="Q89" t="s">
         <v>69</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S89" t="s">
+        <v>27</v>
+      </c>
+      <c r="T89" t="s">
+        <v>96</v>
+      </c>
+      <c r="U89" t="s">
+        <v>97</v>
+      </c>
+      <c r="V89" s="7">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="W89" s="9">
+        <v>0.11458333333333333</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>57</v>
       </c>
@@ -5747,14 +7066,25 @@
       <c r="O90" t="b">
         <v>0</v>
       </c>
+      <c r="P90" t="b">
+        <v>0</v>
+      </c>
       <c r="Q90" t="s">
-        <v>88</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+      <c r="S90" t="s">
+        <v>102</v>
+      </c>
+      <c r="V90" s="7"/>
+      <c r="W90" s="7"/>
       <c r="X90" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>58</v>
       </c>
@@ -5794,14 +7124,29 @@
       <c r="O91" t="b">
         <v>0</v>
       </c>
+      <c r="P91" t="b">
+        <v>0</v>
+      </c>
       <c r="Q91" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V91" s="7">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="W91" s="7">
+        <v>0.45277777777777778</v>
       </c>
       <c r="X91" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>59</v>
       </c>
@@ -5841,14 +7186,25 @@
       <c r="O92" t="b">
         <v>0</v>
       </c>
+      <c r="P92" t="b">
+        <v>0</v>
+      </c>
       <c r="Q92" t="s">
-        <v>89</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92" t="s">
+        <v>102</v>
+      </c>
+      <c r="V92" s="7"/>
+      <c r="W92" s="7"/>
       <c r="X92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>60</v>
       </c>
@@ -5888,14 +7244,29 @@
       <c r="O93" t="b">
         <v>0</v>
       </c>
+      <c r="P93" t="b">
+        <v>0</v>
+      </c>
       <c r="Q93" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" t="s">
+        <v>102</v>
+      </c>
+      <c r="V93" s="7">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="W93" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>61</v>
       </c>
@@ -5935,14 +7306,25 @@
       <c r="O94" t="b">
         <v>0</v>
       </c>
+      <c r="P94" t="b">
+        <v>0</v>
+      </c>
       <c r="Q94" t="s">
-        <v>88</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V94" s="7"/>
+      <c r="W94" s="7"/>
       <c r="X94" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>62</v>
       </c>
@@ -5982,14 +7364,29 @@
       <c r="O95" t="b">
         <v>0</v>
       </c>
+      <c r="P95" t="b">
+        <v>0</v>
+      </c>
       <c r="Q95" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+      <c r="S95" t="s">
+        <v>102</v>
+      </c>
+      <c r="V95" s="7">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="W95" s="7">
+        <v>0.45277777777777778</v>
       </c>
       <c r="X95" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>63</v>
       </c>
@@ -6029,14 +7426,25 @@
       <c r="O96" t="b">
         <v>0</v>
       </c>
+      <c r="P96" t="b">
+        <v>0</v>
+      </c>
       <c r="Q96" t="s">
-        <v>88</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+      <c r="S96" t="s">
+        <v>102</v>
+      </c>
+      <c r="V96" s="7"/>
+      <c r="W96" s="7"/>
       <c r="X96" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>64</v>
       </c>
@@ -6076,14 +7484,29 @@
       <c r="O97" t="b">
         <v>0</v>
       </c>
+      <c r="P97" t="b">
+        <v>0</v>
+      </c>
       <c r="Q97" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+      <c r="S97" t="s">
+        <v>102</v>
+      </c>
+      <c r="V97" s="7">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="W97" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X97" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>65</v>
       </c>
@@ -6123,14 +7546,29 @@
       <c r="O98" t="b">
         <v>0</v>
       </c>
+      <c r="P98" t="b">
+        <v>0</v>
+      </c>
       <c r="Q98" t="s">
-        <v>89</v>
+        <v>106</v>
+      </c>
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
+      <c r="S98" t="s">
+        <v>102</v>
+      </c>
+      <c r="V98" s="7">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="W98" s="7">
+        <v>0.47222222222222221</v>
       </c>
       <c r="X98" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>66</v>
       </c>
@@ -6170,14 +7608,29 @@
       <c r="O99" t="b">
         <v>0</v>
       </c>
+      <c r="P99" t="b">
+        <v>0</v>
+      </c>
       <c r="Q99" t="s">
-        <v>90</v>
+        <v>108</v>
+      </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
+      <c r="S99" t="s">
+        <v>102</v>
+      </c>
+      <c r="V99" s="7">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="W99" s="7">
+        <v>0.4909722222222222</v>
       </c>
       <c r="X99" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>67</v>
       </c>
@@ -6217,14 +7670,29 @@
       <c r="O100" t="b">
         <v>0</v>
       </c>
+      <c r="P100" t="b">
+        <v>0</v>
+      </c>
       <c r="Q100" t="s">
-        <v>90</v>
+        <v>108</v>
+      </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
+      <c r="S100" t="s">
+        <v>102</v>
+      </c>
+      <c r="V100" s="7">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="W100" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>68</v>
       </c>
@@ -6264,14 +7732,29 @@
       <c r="O101" t="b">
         <v>0</v>
       </c>
+      <c r="P101" t="b">
+        <v>0</v>
+      </c>
       <c r="Q101" t="s">
-        <v>90</v>
+        <v>108</v>
+      </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
+      <c r="S101" t="s">
+        <v>102</v>
+      </c>
+      <c r="V101" s="7">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="W101" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X101" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>69</v>
       </c>
@@ -6311,14 +7794,29 @@
       <c r="O102" t="b">
         <v>0</v>
       </c>
+      <c r="P102" t="b">
+        <v>0</v>
+      </c>
       <c r="Q102" t="s">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
+      <c r="S102" t="s">
+        <v>102</v>
+      </c>
+      <c r="V102" s="7">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="W102" s="7">
+        <v>0.47222222222222221</v>
       </c>
       <c r="X102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>70</v>
       </c>
@@ -6358,14 +7856,29 @@
       <c r="O103" t="b">
         <v>0</v>
       </c>
+      <c r="P103" t="b">
+        <v>0</v>
+      </c>
       <c r="Q103" t="s">
-        <v>90</v>
+        <v>112</v>
+      </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
+      <c r="S103" t="s">
+        <v>102</v>
+      </c>
+      <c r="V103" s="7">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="W103" s="7">
+        <v>0.4909722222222222</v>
       </c>
       <c r="X103" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>71</v>
       </c>
@@ -6405,14 +7918,29 @@
       <c r="O104" t="b">
         <v>0</v>
       </c>
+      <c r="P104" t="b">
+        <v>0</v>
+      </c>
       <c r="Q104" t="s">
-        <v>89</v>
+        <v>106</v>
+      </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
+      <c r="S104" t="s">
+        <v>102</v>
+      </c>
+      <c r="V104" s="7">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="W104" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X104" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>72</v>
       </c>
@@ -6452,14 +7980,29 @@
       <c r="O105" t="b">
         <v>0</v>
       </c>
+      <c r="P105" t="b">
+        <v>0</v>
+      </c>
       <c r="Q105" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
+      <c r="S105" t="s">
+        <v>102</v>
+      </c>
+      <c r="V105" s="7">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="W105" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="X105" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>73</v>
       </c>
@@ -6469,7 +8012,7 @@
       <c r="C106">
         <v>6</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E106" s="3">
         <v>45660</v>
       </c>
       <c r="F106" t="s">
@@ -6499,8 +8042,35 @@
       <c r="O106" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P106" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>66</v>
+      </c>
+      <c r="R106" t="b">
+        <v>0</v>
+      </c>
+      <c r="S106" t="s">
+        <v>27</v>
+      </c>
+      <c r="T106" t="s">
+        <v>96</v>
+      </c>
+      <c r="U106" t="s">
+        <v>97</v>
+      </c>
+      <c r="V106" s="7">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="W106" s="7">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="X106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>74</v>
       </c>
@@ -6510,7 +8080,7 @@
       <c r="C107">
         <v>6</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E107" s="3">
         <v>45660</v>
       </c>
       <c r="F107" t="s">
@@ -6540,8 +8110,35 @@
       <c r="O107" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P107" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>66</v>
+      </c>
+      <c r="R107" t="b">
+        <v>0</v>
+      </c>
+      <c r="S107" t="s">
+        <v>27</v>
+      </c>
+      <c r="T107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U107" t="s">
+        <v>97</v>
+      </c>
+      <c r="V107" s="7">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="W107" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X107" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>75</v>
       </c>
@@ -6551,7 +8148,7 @@
       <c r="C108">
         <v>6</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E108" s="3">
         <v>45660</v>
       </c>
       <c r="F108" t="s">
@@ -6581,8 +8178,35 @@
       <c r="O108" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P108" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>66</v>
+      </c>
+      <c r="R108" t="b">
+        <v>0</v>
+      </c>
+      <c r="S108" t="s">
+        <v>27</v>
+      </c>
+      <c r="T108" t="s">
+        <v>96</v>
+      </c>
+      <c r="U108" t="s">
+        <v>97</v>
+      </c>
+      <c r="V108" s="7">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="W108" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X108" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>76</v>
       </c>
@@ -6592,7 +8216,7 @@
       <c r="C109">
         <v>6</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="3">
         <v>45660</v>
       </c>
       <c r="F109" t="s">
@@ -6622,8 +8246,35 @@
       <c r="O109" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P109" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>66</v>
+      </c>
+      <c r="R109" t="b">
+        <v>0</v>
+      </c>
+      <c r="S109" t="s">
+        <v>27</v>
+      </c>
+      <c r="T109" t="s">
+        <v>96</v>
+      </c>
+      <c r="U109" t="s">
+        <v>97</v>
+      </c>
+      <c r="V109" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W109" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X109" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>77</v>
       </c>
@@ -6633,7 +8284,7 @@
       <c r="C110">
         <v>6</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E110" s="3">
         <v>45660</v>
       </c>
       <c r="F110" t="s">
@@ -6663,8 +8314,35 @@
       <c r="O110" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P110" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>66</v>
+      </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
+      <c r="S110" t="s">
+        <v>27</v>
+      </c>
+      <c r="T110" t="s">
+        <v>96</v>
+      </c>
+      <c r="U110" t="s">
+        <v>97</v>
+      </c>
+      <c r="V110" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W110" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="X110" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>78</v>
       </c>
@@ -6674,7 +8352,7 @@
       <c r="C111">
         <v>6</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E111" s="3">
         <v>45660</v>
       </c>
       <c r="F111" t="s">
@@ -6704,8 +8382,35 @@
       <c r="O111" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P111" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>66</v>
+      </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
+      <c r="S111" t="s">
+        <v>27</v>
+      </c>
+      <c r="T111" t="s">
+        <v>96</v>
+      </c>
+      <c r="U111" t="s">
+        <v>97</v>
+      </c>
+      <c r="V111" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="W111" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="X111" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>79</v>
       </c>
@@ -6715,7 +8420,7 @@
       <c r="C112">
         <v>6</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="3">
         <v>45660</v>
       </c>
       <c r="F112" t="s">
@@ -6745,8 +8450,35 @@
       <c r="O112" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P112" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>66</v>
+      </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
+      <c r="S112" t="s">
+        <v>27</v>
+      </c>
+      <c r="T112" t="s">
+        <v>96</v>
+      </c>
+      <c r="U112" t="s">
+        <v>97</v>
+      </c>
+      <c r="V112" s="7">
+        <v>0.40625</v>
+      </c>
+      <c r="W112" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X112" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>80</v>
       </c>
@@ -6756,7 +8488,7 @@
       <c r="C113">
         <v>6</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="3">
         <v>45660</v>
       </c>
       <c r="F113" t="s">
@@ -6786,8 +8518,35 @@
       <c r="O113" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P113" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>66</v>
+      </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
+      <c r="S113" t="s">
+        <v>27</v>
+      </c>
+      <c r="T113" t="s">
+        <v>96</v>
+      </c>
+      <c r="U113" t="s">
+        <v>97</v>
+      </c>
+      <c r="V113" s="7">
+        <v>0.40625</v>
+      </c>
+      <c r="W113" s="7">
+        <v>0.46875</v>
+      </c>
+      <c r="X113" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>81</v>
       </c>
@@ -6797,7 +8556,7 @@
       <c r="C114">
         <v>6</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E114" s="3">
         <v>45660</v>
       </c>
       <c r="F114" t="s">
@@ -6827,8 +8586,35 @@
       <c r="O114" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P114" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>66</v>
+      </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
+      <c r="S114" t="s">
+        <v>27</v>
+      </c>
+      <c r="T114" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="U114" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="V114" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="W114" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="X114" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>82</v>
       </c>
@@ -6838,7 +8624,7 @@
       <c r="C115">
         <v>6</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="3">
         <v>45660</v>
       </c>
       <c r="F115" t="s">
@@ -6868,8 +8654,35 @@
       <c r="O115" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P115" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>66</v>
+      </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
+      <c r="S115" t="s">
+        <v>27</v>
+      </c>
+      <c r="T115" t="s">
+        <v>96</v>
+      </c>
+      <c r="U115" t="s">
+        <v>97</v>
+      </c>
+      <c r="V115" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W115" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="X115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>83</v>
       </c>
@@ -6879,7 +8692,7 @@
       <c r="C116">
         <v>6</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E116" s="3">
         <v>45660</v>
       </c>
       <c r="F116" t="s">
@@ -6909,8 +8722,35 @@
       <c r="O116" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P116" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>66</v>
+      </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
+      <c r="S116" t="s">
+        <v>27</v>
+      </c>
+      <c r="T116" t="s">
+        <v>96</v>
+      </c>
+      <c r="U116" t="s">
+        <v>97</v>
+      </c>
+      <c r="V116" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W116" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="X116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>84</v>
       </c>
@@ -6920,7 +8760,7 @@
       <c r="C117">
         <v>6</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="3">
         <v>45660</v>
       </c>
       <c r="F117" t="s">
@@ -6950,8 +8790,35 @@
       <c r="O117" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P117" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>66</v>
+      </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
+      <c r="S117" t="s">
+        <v>27</v>
+      </c>
+      <c r="T117" t="s">
+        <v>96</v>
+      </c>
+      <c r="U117" t="s">
+        <v>97</v>
+      </c>
+      <c r="V117" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="W117" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X117" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>85</v>
       </c>
@@ -6961,7 +8828,7 @@
       <c r="C118">
         <v>6</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="3">
         <v>45660</v>
       </c>
       <c r="F118" t="s">
@@ -6991,8 +8858,35 @@
       <c r="O118" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P118" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>66</v>
+      </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
+      <c r="S118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T118" t="s">
+        <v>96</v>
+      </c>
+      <c r="U118" t="s">
+        <v>97</v>
+      </c>
+      <c r="V118" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="W118" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X118" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>86</v>
       </c>
@@ -7002,7 +8896,7 @@
       <c r="C119">
         <v>6</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="3">
         <v>45660</v>
       </c>
       <c r="F119" t="s">
@@ -7032,8 +8926,35 @@
       <c r="O119" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P119" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>66</v>
+      </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
+      <c r="S119" t="s">
+        <v>27</v>
+      </c>
+      <c r="T119" t="s">
+        <v>96</v>
+      </c>
+      <c r="U119" t="s">
+        <v>97</v>
+      </c>
+      <c r="V119" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="W119" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="X119" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>87</v>
       </c>
@@ -7043,7 +8964,7 @@
       <c r="C120">
         <v>6</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="3">
         <v>45660</v>
       </c>
       <c r="F120" t="s">
@@ -7073,8 +8994,35 @@
       <c r="O120" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P120" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>66</v>
+      </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
+      <c r="S120" t="s">
+        <v>27</v>
+      </c>
+      <c r="T120" t="s">
+        <v>96</v>
+      </c>
+      <c r="U120" t="s">
+        <v>97</v>
+      </c>
+      <c r="V120" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="W120" s="7">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="X120" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>88</v>
       </c>
@@ -7084,7 +9032,7 @@
       <c r="C121">
         <v>6</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="3">
         <v>45660</v>
       </c>
       <c r="F121" t="s">
@@ -7114,8 +9062,35 @@
       <c r="O121" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P121" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>66</v>
+      </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
+      <c r="S121" t="s">
+        <v>27</v>
+      </c>
+      <c r="T121" t="s">
+        <v>96</v>
+      </c>
+      <c r="U121" t="s">
+        <v>97</v>
+      </c>
+      <c r="V121" s="7">
+        <v>0.46875</v>
+      </c>
+      <c r="W121" s="7">
+        <v>0.53125</v>
+      </c>
+      <c r="X121" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>89</v>
       </c>
@@ -7125,7 +9100,7 @@
       <c r="C122">
         <v>6</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="3">
         <v>45660</v>
       </c>
       <c r="F122" t="s">
@@ -7155,8 +9130,35 @@
       <c r="O122" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P122" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>66</v>
+      </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
+      <c r="S122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T122" t="s">
+        <v>96</v>
+      </c>
+      <c r="U122" t="s">
+        <v>97</v>
+      </c>
+      <c r="V122" s="7">
+        <v>0.46875</v>
+      </c>
+      <c r="W122" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X122" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>90</v>
       </c>
@@ -7166,7 +9168,7 @@
       <c r="C123">
         <v>6</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="3">
         <v>45660</v>
       </c>
       <c r="F123" t="s">
@@ -7196,8 +9198,35 @@
       <c r="O123" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P123" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>66</v>
+      </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
+      <c r="S123" t="s">
+        <v>27</v>
+      </c>
+      <c r="T123" t="s">
+        <v>96</v>
+      </c>
+      <c r="U123" t="s">
+        <v>97</v>
+      </c>
+      <c r="V123" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="W123" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="X123" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>91</v>
       </c>
@@ -7207,7 +9236,7 @@
       <c r="C124">
         <v>6</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="3">
         <v>45660</v>
       </c>
       <c r="F124" t="s">
@@ -7237,8 +9266,35 @@
       <c r="O124" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P124" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>66</v>
+      </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
+      <c r="S124" t="s">
+        <v>27</v>
+      </c>
+      <c r="T124" t="s">
+        <v>96</v>
+      </c>
+      <c r="U124" t="s">
+        <v>97</v>
+      </c>
+      <c r="V124" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="W124" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X124" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>92</v>
       </c>
@@ -7248,7 +9304,7 @@
       <c r="C125">
         <v>6</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E125" s="3">
         <v>45660</v>
       </c>
       <c r="F125" t="s">
@@ -7278,8 +9334,35 @@
       <c r="O125" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P125" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>66</v>
+      </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
+      <c r="S125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T125" t="s">
+        <v>96</v>
+      </c>
+      <c r="U125" t="s">
+        <v>97</v>
+      </c>
+      <c r="V125" s="7">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="W125" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="X125" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>93</v>
       </c>
@@ -7289,7 +9372,7 @@
       <c r="C126">
         <v>6</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="3">
         <v>45660</v>
       </c>
       <c r="F126" t="s">
@@ -7319,8 +9402,35 @@
       <c r="O126" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P126" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>66</v>
+      </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
+      <c r="S126" t="s">
+        <v>27</v>
+      </c>
+      <c r="T126" t="s">
+        <v>96</v>
+      </c>
+      <c r="U126" t="s">
+        <v>97</v>
+      </c>
+      <c r="V126" s="7">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="W126" s="7">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="X126" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>94</v>
       </c>
@@ -7330,7 +9440,7 @@
       <c r="C127">
         <v>6</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E127" s="3">
         <v>45660</v>
       </c>
       <c r="F127" t="s">
@@ -7360,8 +9470,35 @@
       <c r="O127" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P127" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>66</v>
+      </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
+      <c r="S127" t="s">
+        <v>27</v>
+      </c>
+      <c r="T127" t="s">
+        <v>96</v>
+      </c>
+      <c r="U127" t="s">
+        <v>97</v>
+      </c>
+      <c r="V127" s="7">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="W127" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X127" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>95</v>
       </c>
@@ -7371,7 +9508,7 @@
       <c r="C128">
         <v>6</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E128" s="3">
         <v>45660</v>
       </c>
       <c r="F128" t="s">
@@ -7401,10 +9538,37 @@
       <c r="O128" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>73</v>
+      <c r="P128" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>66</v>
+      </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
+      <c r="S128" t="s">
+        <v>27</v>
+      </c>
+      <c r="T128" t="s">
+        <v>96</v>
+      </c>
+      <c r="U128" t="s">
+        <v>97</v>
+      </c>
+      <c r="V128" s="7">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="W128" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X128" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="B129">
         <v>128</v>
@@ -7412,10 +9576,10 @@
       <c r="C129">
         <v>7</v>
       </c>
-      <c r="D129" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E129" s="8">
+      <c r="D129" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E129" s="5">
         <v>45688</v>
       </c>
       <c r="F129" t="s">
@@ -7445,13 +9609,22 @@
       <c r="O129" t="b">
         <v>0</v>
       </c>
+      <c r="P129" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>66</v>
+      </c>
+      <c r="R129" t="b">
+        <v>0</v>
+      </c>
       <c r="X129" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B130">
         <v>129</v>
@@ -7459,10 +9632,10 @@
       <c r="C130">
         <v>7</v>
       </c>
-      <c r="D130" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E130" s="8">
+      <c r="D130" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E130" s="5">
         <v>45688</v>
       </c>
       <c r="F130" t="s">
@@ -7492,13 +9665,22 @@
       <c r="O130" t="b">
         <v>0</v>
       </c>
+      <c r="P130" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>66</v>
+      </c>
+      <c r="R130" t="b">
+        <v>0</v>
+      </c>
       <c r="X130" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
-        <v>75</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B131">
         <v>130</v>
@@ -7506,10 +9688,10 @@
       <c r="C131">
         <v>7</v>
       </c>
-      <c r="D131" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E131" s="8">
+      <c r="D131" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E131" s="5">
         <v>45688</v>
       </c>
       <c r="F131" t="s">
@@ -7539,16 +9721,22 @@
       <c r="O131" t="b">
         <v>0</v>
       </c>
+      <c r="P131" t="b">
+        <v>0</v>
+      </c>
       <c r="Q131" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="R131" t="b">
+        <v>0</v>
       </c>
       <c r="X131" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
-        <v>76</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B132">
         <v>131</v>
@@ -7556,10 +9744,10 @@
       <c r="C132">
         <v>7</v>
       </c>
-      <c r="D132" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E132" s="8">
+      <c r="D132" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E132" s="5">
         <v>45713</v>
       </c>
       <c r="F132" t="s">
@@ -7589,16 +9777,22 @@
       <c r="O132" t="b">
         <v>0</v>
       </c>
+      <c r="P132" t="b">
+        <v>0</v>
+      </c>
       <c r="Q132" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="R132" t="b">
+        <v>0</v>
       </c>
       <c r="X132" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B133">
         <v>132</v>
@@ -7606,10 +9800,10 @@
       <c r="C133">
         <v>7</v>
       </c>
-      <c r="D133" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E133" s="8">
+      <c r="D133" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E133" s="5">
         <v>45713</v>
       </c>
       <c r="F133" t="s">
@@ -7639,13 +9833,22 @@
       <c r="O133" t="b">
         <v>0</v>
       </c>
+      <c r="P133" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>66</v>
+      </c>
+      <c r="R133" t="b">
+        <v>0</v>
+      </c>
       <c r="X133" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="B134">
         <v>133</v>
@@ -7653,10 +9856,10 @@
       <c r="C134">
         <v>7</v>
       </c>
-      <c r="D134" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E134" s="8">
+      <c r="D134" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E134" s="5">
         <v>45713</v>
       </c>
       <c r="F134" t="s">
@@ -7686,13 +9889,22 @@
       <c r="O134" t="b">
         <v>0</v>
       </c>
+      <c r="P134" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>66</v>
+      </c>
+      <c r="R134" t="b">
+        <v>0</v>
+      </c>
       <c r="X134" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="B135">
         <v>134</v>
@@ -7700,10 +9912,10 @@
       <c r="C135">
         <v>7</v>
       </c>
-      <c r="D135" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E135" s="8">
+      <c r="D135" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E135" s="5">
         <v>45713</v>
       </c>
       <c r="F135" t="s">
@@ -7733,13 +9945,22 @@
       <c r="O135" t="b">
         <v>0</v>
       </c>
+      <c r="P135" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>66</v>
+      </c>
+      <c r="R135" t="b">
+        <v>0</v>
+      </c>
       <c r="X135" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
-        <v>80</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="B136">
         <v>135</v>
@@ -7747,10 +9968,10 @@
       <c r="C136">
         <v>7</v>
       </c>
-      <c r="D136" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E136" s="8">
+      <c r="D136" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E136" s="5">
         <v>45713</v>
       </c>
       <c r="F136" t="s">
@@ -7780,13 +10001,22 @@
       <c r="O136" t="b">
         <v>0</v>
       </c>
+      <c r="P136" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>66</v>
+      </c>
+      <c r="R136" t="b">
+        <v>0</v>
+      </c>
       <c r="X136" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B137">
         <v>136</v>
@@ -7794,10 +10024,10 @@
       <c r="C137">
         <v>7</v>
       </c>
-      <c r="D137" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E137" s="8">
+      <c r="D137" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E137" s="5">
         <v>45713</v>
       </c>
       <c r="F137" t="s">
@@ -7827,13 +10057,22 @@
       <c r="O137" t="b">
         <v>0</v>
       </c>
+      <c r="P137" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>66</v>
+      </c>
+      <c r="R137" t="b">
+        <v>0</v>
+      </c>
       <c r="X137" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="B138">
         <v>137</v>
@@ -7841,10 +10080,10 @@
       <c r="C138">
         <v>7</v>
       </c>
-      <c r="D138" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E138" s="8">
+      <c r="D138" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E138" s="5">
         <v>45713</v>
       </c>
       <c r="F138" t="s">
@@ -7874,13 +10113,22 @@
       <c r="O138" t="b">
         <v>0</v>
       </c>
+      <c r="P138" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>66</v>
+      </c>
+      <c r="R138" t="b">
+        <v>0</v>
+      </c>
       <c r="X138" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B139">
         <v>138</v>
@@ -7888,10 +10136,10 @@
       <c r="C139">
         <v>7</v>
       </c>
-      <c r="D139" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E139" s="8">
+      <c r="D139" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E139" s="5">
         <v>45713</v>
       </c>
       <c r="F139" t="s">
@@ -7921,13 +10169,22 @@
       <c r="O139" t="b">
         <v>0</v>
       </c>
+      <c r="P139" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>66</v>
+      </c>
+      <c r="R139" t="b">
+        <v>0</v>
+      </c>
       <c r="X139" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="B140">
         <v>139</v>
@@ -7935,10 +10192,10 @@
       <c r="C140">
         <v>7</v>
       </c>
-      <c r="D140" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E140" s="8">
+      <c r="D140" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E140" s="5">
         <v>45713</v>
       </c>
       <c r="F140" t="s">
@@ -7968,8 +10225,17 @@
       <c r="O140" t="b">
         <v>0</v>
       </c>
+      <c r="P140" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>66</v>
+      </c>
+      <c r="R140" t="b">
+        <v>0</v>
+      </c>
       <c r="X140" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
